--- a/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va raconter. Même si on a ri. Il dit : maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri. Naël respire.</t>
+          <t>Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va raconter. Même si on a ri. Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri. Naël respire.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va raconter. Même si on a ri.
+narrateur|Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.
+narrateur|Naël respire.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Naël a ri à l'école. Que fait-il à la maison ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Naël a raconté. Même s'il a ri. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prépare le goûter. Naël s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Naël respire.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Naël a ri à l'école. Que fait-il à la maison ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Naël a raconté. Même s'il a ri. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Maman prépare le goûter. Naël s'assoit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Naël raconte, même s'il a ri</t>
+          <t>Le cacao d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon jaune traverse le tapis. Aniss rentre, ventre serré. Même s'il a ri à l'école, il raconte à maman et papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va raconter. Même si on a ri. Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri. Naël respire.</t>
+          <t>Un rayon jaune traverse le tapis. Il est chaud, tout long, comme un chemin. Le cacao fume dans la tasse bleue. Ça sent le chocolat et le lait. Un foulard jaune attend sur la chaise. La pendule fait tic, tout doux. Dehors, un oiseau chante près de la haie. La tasse bleue a un petit éclat, près de l'anse. Le foulard est doux, un peu rêche au bord. Le cacao est prêt, Aniss. Tes chaussures sont dans l'entrée. Viens. En ce moment, Aniss rentre de l'école. Son cartable pose un bruit sourd contre le mur. Ses joues sont chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires, un court moment. Aniss a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Assieds-toi près du rayon. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Aniss ne répète pas les mots. Il parle tout bas. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Aniss souffle. Ses épaules descendent. Bravo, Aniss. C'est du bon travail. Tu as dit ce qui s'est passé. Tu veux ton cacao ? Oui, maman. La tasse est chaude entre ses mains. Le rayon avance un peu sur le tapis. On reste encore un peu ensemble ? Oui, papa. Le foulard jaune t'attend, après. Aniss boit une gorgée. Il se sent plus léger. La pendule continue son tic doux. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le cacao laisse un cercle brun dans la tasse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va raconter. Même si on a ri.
-narrateur|Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.
-narrateur|Naël respire.</t>
+          <t>narrateur|Un rayon jaune traverse le tapis.
+narrateur|Il est chaud, tout long, comme un chemin.
+narrateur|Le cacao fume dans la tasse bleue.
+narrateur|Ça sent le chocolat et le lait.
+narrateur|Un foulard jaune attend sur la chaise.
+narrateur|La pendule fait tic, tout doux.
+narrateur|Dehors, un oiseau chante près de la haie.
+narrateur|La tasse bleue a un petit éclat, près de l'anse.
+narrateur|Le foulard est doux, un peu rêche au bord.
+maman|Le cacao est prêt, Aniss.
+papa|Tes chaussures sont dans l'entrée.
+papa|Viens.
+narrateur|En ce moment, Aniss rentre de l'école.
+narrateur|Son cartable pose un bruit sourd contre le mur.
+narrateur|Ses joues sont chaudes.
+narrateur|Son ventre est serré.
+narrateur|À l'école, un bonnet est tombé par terre.
+narrateur|Il y a eu des rires, un court moment.
+narrateur|Aniss a ri un peu aussi.
+enfant-m|Maman.
+enfant-m|J'ai ri.
+enfant-m|Ce n'était pas gentil.
+maman|Je t'écoute.
+maman|Assieds-toi près du rayon.
+papa|Moi aussi, je t'écoute.
+papa|Tu peux raconter.
+papa|Raconter, c'est dire ce qui s'est passé.
+enfant-m|Un bonnet est tombé.
+enfant-m|On a ri.
+enfant-m|J'ai ri un peu.
+narrateur|Aniss ne répète pas les mots.
+narrateur|Il parle tout bas.
+maman|Même si tu as ri, tu racontes.
+papa|Même si on a ri, on raconte à papa ou maman.
+maman|Merci d'avoir raconté.
+papa|On est là.
+enfant-m|Mon ventre est encore un peu serré.
+maman|Souffle un peu.
+narrateur|Aniss souffle.
+narrateur|Ses épaules descendent.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+maman|Tu as dit ce qui s'est passé.
+maman|Tu veux ton cacao ?
+enfant-m|Oui, maman.
+narrateur|La tasse est chaude entre ses mains.
+narrateur|Le rayon avance un peu sur le tapis.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui, papa.
+maman|Le foulard jaune t'attend, après.
+narrateur|Aniss boit une gorgée.
+narrateur|Il se sent plus léger.
+narrateur|La pendule continue son tic doux.
+maman|Tu as raconté.
+maman|Même si tu as ri.
+enfant-m|Oui, maman.
+papa|On est là, ce soir aussi.
+narrateur|Le cacao laisse un cercle brun dans la tasse.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Naël a ri à l'école. Que fait-il à la maison ?</t>
+          <t>Aniss a ri à l'école. Que fait-il à la maison ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Naël a ri à l'école. Que fait-il à la maison ?</t>
+          <t>narrateur|Aniss a ri à l'école.
+narrateur|Que fait-il à la maison ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Naël a raconté. Même s'il a ri. Papa et maman ont écouté.</t>
+          <t>Aniss a raconté. Même s'il a ri. Papa et maman ont écouté. Tu es venu nous le dire. Bravo. C'est du bon travail, Aniss. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le cacao n'est plus tout à fait fumant. Le ventre d'Aniss se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1738,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Naël a raconté. Même s'il a ri. Papa et maman ont écouté.</t>
+          <t>narrateur|Aniss a raconté.
+narrateur|Même s'il a ri.
+narrateur|Papa et maman ont écouté.
+maman|Tu es venu nous le dire.
+maman|Bravo.
+papa|C'est du bon travail, Aniss.
+enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+papa|Oui.
+papa|On raconte à papa ou maman.
+narrateur|Le cacao n'est plus tout à fait fumant.
+narrateur|Le ventre d'Aniss se desserre.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prépare le goûter. Naël s'assoit.</t>
+          <t>Maman prépare le goûter. Une tranche sent encore le pain chaud. Tu t'assois ? Oui. Aniss s'assoit. Le rayon touche maintenant ses chaussettes. Le cacao t'a réchauffé ? Oui, papa. On t'écoute encore, si tu veux. J'ai déjà raconté. C'est bien. La tasse bleue reste près de sa main.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1913,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prépare le goûter. Naël s'assoit.</t>
+          <t>narrateur|Maman prépare le goûter.
+narrateur|Une tranche sent encore le pain chaud.
+maman|Tu t'assois ?
+enfant-m|Oui.
+narrateur|Aniss s'assoit.
+narrateur|Le rayon touche maintenant ses chaussettes.
+papa|Le cacao t'a réchauffé ?
+enfant-m|Oui, papa.
+maman|On t'écoute encore, si tu veux.
+enfant-m|J'ai déjà raconté.
+papa|C'est bien.
+narrateur|La tasse bleue reste près de sa main.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. Le rayon jaune a glissé jusqu'à la chaise. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2092,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté à la maison.
+enfant-m|Même si j'ai ri.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|On t'a écouté.
+narrateur|Le rayon jaune a glissé jusqu'à la chaise.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune traverse le tapis. Il est chaud, tout long, comme un chemin. Le cacao fume dans la tasse bleue. Ça sent le chocolat et le lait. Un foulard jaune attend sur la chaise. La pendule fait tic, tout doux. Dehors, un oiseau chante près de la haie. La tasse bleue a un petit éclat, près de l'anse. Le foulard est doux, un peu rêche au bord. Le cacao est prêt, Aniss. Tes chaussures sont dans l'entrée. Viens. En ce moment, Aniss rentre de l'école. Son cartable pose un bruit sourd contre le mur. Ses joues sont chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires, un court moment. Aniss a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Assieds-toi près du rayon. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Aniss ne répète pas les mots. Il parle tout bas. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Aniss souffle. Ses épaules descendent. Bravo, Aniss. C'est du bon travail. Tu as dit ce qui s'est passé. Tu veux ton cacao ? Oui, maman. La tasse est chaude entre ses mains. Le rayon avance un peu sur le tapis. On reste encore un peu ensemble ? Oui, papa. Le foulard jaune t'attend, après. Aniss boit une gorgée. Il se sent plus léger. La pendule continue son tic doux. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le cacao laisse un cercle brun dans la tasse.</t>
+          <t>Un rayon jaune traverse le tapis. Il est chaud, tout long, comme un chemin. Le cacao fume dans la tasse bleue. Ça sent le chocolat et le lait. Un foulard jaune attend sur la chaise. La pendule fait tic, tout doux. Dehors, un oiseau chante près de la haie. La tasse bleue a un petit éclat, près de l'anse. Le foulard est doux, un peu rêche au bord. Le cacao est prêt, Aniss. Tes chaussures sont dans l'entrée. Viens. En ce moment, Aniss rentre de l'école. Son cartable pose un bruit sourd contre le mur. Ses joues sont chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires, un court moment. Aniss a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Assieds-toi près du rayon. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Aniss ne répète pas les mots. Il parle tout bas. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Aniss souffle. Ses épaules descendent. Bravo, Aniss. Tu as dit ce qui s'est passé. Tu veux ton cacao ? Oui, maman. La tasse est chaude entre ses mains. Le rayon avance un peu sur le tapis. On reste encore un peu ensemble ? Oui, papa. Le foulard jaune t'attend, après. Aniss boit une gorgée. Il se sent plus léger. La pendule continue son tic doux. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le cacao laisse un cercle brun dans la tasse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël rentre. À l'école, un camarade a fait tomber son bonnet. Naël a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Naël va &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri. Il dit : maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri. Naël respire.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune traverse le tapis. Il est chaud, tout long, comme un chemin. Le cacao fume dans la tasse bleue. Ça sent le chocolat et le lait. Un foulard jaune attend sur la chaise. La pendule fait tic, tout doux. Dehors, un oiseau chante près de la haie. La tasse bleue a un petit éclat, près de l'anse. Le foulard est doux, un peu rêche au bord. Le cacao est prêt, Aniss. Tes chaussures sont dans l'entrée. Viens. En ce moment, Aniss rentre de l'école. Son cartable pose un bruit sourd contre le mur. Ses joues sont chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires, un court moment. Aniss a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Assieds-toi près du rayon. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Aniss ne répète pas les mots. Il parle tout bas. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Aniss souffle. Ses épaules descendent. Bravo, Aniss. Tu as dit ce qui s'est passé. Tu veux ton cacao ? Oui, maman. La tasse est chaude entre ses mains. Le rayon avance un peu sur le tapis. On reste encore un peu ensemble ? Oui, papa. Le foulard jaune t'attend, après. Aniss boit une gorgée. Il se sent plus léger. La pendule continue son tic doux. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le cacao laisse un cercle brun dans la tasse.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 narrateur|Aniss souffle.
 narrateur|Ses épaules descendent.
 papa|Bravo, Aniss.
-papa|C'est du bon travail.
 maman|Tu as dit ce qui s'est passé.
 maman|Tu veux ton cacao ?
 enfant-m|Oui, maman.
@@ -1384,7 +1383,6 @@
 narrateur|Le cacao laisse un cercle brun dans la tasse.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël a ri à l'école. Que fait-il à la maison ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a ri à l'école. Que fait-il à la maison ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que fait-il à la maison ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a raconté. Même s'il a ri. Papa et maman ont écouté. Tu es venu nous le dire. Bravo. C'est du bon travail, Aniss. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le cacao n'est plus tout à fait fumant. Le ventre d'Aniss se desserre.</t>
+          <t>Aniss a raconté. Même s'il a ri. Papa et maman ont écouté. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le cacao n'est plus tout à fait fumant. Le ventre d'Aniss se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël a raconté. &lt;emphasis level="moderate"&gt;même&lt;/emphasis&gt; s'il a ri. Papa et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a raconté. Même s'il a ri. Papa et maman ont écouté. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le cacao n'est plus tout à fait fumant. Le ventre d'Aniss se desserre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1740,6 @@
 narrateur|Papa et maman ont écouté.
 maman|Tu es venu nous le dire.
 maman|Bravo.
-papa|C'est du bon travail, Aniss.
 enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 papa|Oui.
@@ -1752,7 +1748,6 @@
 narrateur|Le ventre d'Aniss se desserre.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prépare le goûter. Naël s'assoit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman prépare le goûter. Une tranche sent encore le pain chaud. Tu t'assois ? Oui. Aniss s'assoit. Le rayon touche maintenant ses chaussettes. Le cacao t'a réchauffé ? Oui, papa. On t'écoute encore, si tu veux. J'ai déjà raconté. C'est bien. La tasse bleue reste près de sa main.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1922,6 @@
 narrateur|La tasse bleue reste près de sa main.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. Le rayon jaune a glissé jusqu'à la chaise. L'histoire est finie.</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. On t'a écouté. Le rayon jaune a glissé jusqu'à la chaise.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. On t'a écouté. Le rayon jaune a glissé jusqu'à la chaise.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,13 +2089,10 @@
           <t>enfant-m|J'ai raconté à la maison.
 enfant-m|Même si j'ai ri.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|On t'a écouté.
-narrateur|Le rayon jaune a glissé jusqu'à la chaise.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rayon jaune a glissé jusqu'à la chaise.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Naël, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
